--- a/vorlagen/raumklima-protokoll-schimmelverdacht/raumklima-protokoll-schimmelverdacht.xlsx
+++ b/vorlagen/raumklima-protokoll-schimmelverdacht/raumklima-protokoll-schimmelverdacht.xlsx
@@ -1082,7 +1082,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grundlagen: DIN/TS 4108-8:2022-09, Wärmeschutz und Energie-Einsparung in Gebäuden – Teil 8: Vermeidung von Schimmelwachstum in Wohngebäuden · Umweltbundesamt: Leitfaden zur Vorbeugung, Erfassung und Sanierung von Schimmelbefall in Gebäuden, Dezember 2017, aktualisiert April 2024 · Schmidt/Windhausen: Lohmeyer Praktische Bauphysik, 10. Aufl. 2024, S. 263, 363 und 385 · Vogdt (Hrsg.): Bauphysik. Grundwissen für Architekten, 2022, S. 119 und 129 · Willems (Hrsg.): Lehrbuch der Bauphysik, 9. Aufl. 2022, S. 481 · Hestermann/Rongen: Frick/Knöll Baukonstruktionslehre 1, 37. Aufl. 2025, S. 933 · Umweltbundesamt: Wie lüfte ich richtig? Tipps und Tricks zur Schimmelvermeidung · Verband Privater Bauherren: Lüften, vpb.de · Verbraucherzentrale: Schimmel an der Wand entfernen, verbraucherzentrale.de · Bauherren-Schutzbund: Schimmelbefall durch richtiges Heizen und Lüften vermeiden, bsb-ev.de</t>
+          <t>Grundlagen: DIN/TS 4108-8:2022-09, Wärmeschutz und Energie-Einsparung in Gebäuden – Teil 8: Vermeidung von Schimmelwachstum in Wohngebäuden · Umweltbundesamt: Leitfaden zur Vorbeugung, Erfassung und Sanierung von Schimmelbefall in Gebäuden, Dezember 2017 · Schmidt/Windhausen: Lohmeyer Praktische Bauphysik, 10. Aufl. 2024, S. 263, 363 und 385 · Vogdt (Hrsg.): Bauphysik. Grundwissen für Architekten, 2022, S. 119 · Willems (Hrsg.): Lehrbuch der Bauphysik, 9. Aufl. 2022, S. 481 · Hestermann/Rongen: Frick/Knöll Baukonstruktionslehre 1, 37. Aufl. 2025, S. 933 · Umweltbundesamt: Wie lüfte ich richtig? Tipps und Tricks zur Schimmelvermeidung · Verband Privater Bauherren: Lüften, vpb.de · Verbraucherzentrale: Schimmel an der Wand entfernen, verbraucherzentrale.de · Bauherren-Schutzbund: Schimmelbefall durch richtiges Heizen und Lüften vermeiden, bsb-ev.de</t>
         </is>
       </c>
     </row>
